--- a/public/templates/sru-org-structure-import-template.xlsx
+++ b/public/templates/sru-org-structure-import-template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
   <si>
     <t>نموذج استيراد الموظفين والهيكل التنظيمي — نظام تقييم الأداء (جامعة سليمان الراجحي)</t>
   </si>
@@ -48,7 +48,10 @@
     <t>- "الادارة" في ورقة الموظفين تُطابَق تلقائيًا مع اسم الوحدة التنظيمية الموجود في النظام — الأقسام غير المطابَقة تُترك فارغة وتظهر في تقرير الاستيراد لتصحيحها لاحقًا.</t>
   </si>
   <si>
-    <t>- يمكن إعادة رفع نفس الملف بعد التعديل: يُحدَّث الموظفون بالرقم الوظيفي، وتُحدَّث المناصب بالرمز، ولا يُحذف أي تسكين موجود مسبقًا.</t>
+    <t>- الأدوار المتاحة في عمود "الدور في النظام": الرئيس التنفيذي، رئيس تنفيذي، رئيس مباشر، عميد / مدير، لجنة التقييم، مدير الاستراتيجية، مدير الجدارات، مدير الموارد البشرية، مدير النظام، مرشد، مشرف ميداني، موظف. اتركه فارغًا إن لم ترغب بإسناد دور.</t>
+  </si>
+  <si>
+    <t>- يمكن إعادة رفع نفس الملف بعد التعديل: يُحدَّث الموظفون بالرقم الوظيفي، وتُحدَّث المناصب بالرمز، ولا يُحذف أي تسكين أو دور موجود مسبقًا.</t>
   </si>
   <si>
     <t>EMPLOYEE NUMBER</t>
@@ -105,6 +108,9 @@
     <t>Insurance Category</t>
   </si>
   <si>
+    <t>الدور في النظام</t>
+  </si>
+  <si>
     <t>90010</t>
   </si>
   <si>
@@ -157,6 +163,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>موظف</t>
   </si>
   <si>
     <t>المستوى</t>
@@ -605,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -676,6 +685,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -684,122 +698,128 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="18" width="22" customWidth="1"/>
+    <col min="1" max="19" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -818,36 +838,36 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>1</v>
@@ -858,22 +878,22 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/sru-org-structure-import-template.xlsx
+++ b/public/templates/sru-org-structure-import-template.xlsx
@@ -5,209 +5,88 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="تعليمات" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Employees Data" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="الهيكل التنظيمي" state="visible" r:id="rId6"/>
+    <sheet sheetId="2" name="الهيكل التنظيمي" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
-  <si>
-    <t>نموذج استيراد الموظفين والهيكل التنظيمي — نظام تقييم الأداء (جامعة سليمان الراجحي)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+  <si>
+    <t>نموذج استيراد الهيكل التنظيمي — نظام تقييم الأداء (جامعة سليمان الراجحي)</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>يحتوي هذا الملف على ورقتين للبيانات:</t>
-  </si>
-  <si>
-    <t>1) Employees Data — بيانات الموظفين. الأعمدة الإلزامية: EMPLOYEE NUMBER، اسم الموظف، EMAIL ID. باقي الأعمدة اختيارية.</t>
-  </si>
-  <si>
-    <t>2) الهيكل التنظيمي — المستويات والمناصب والتسكين. الأعمدة الإلزامية: المستوى، الرمز، الوحدة التنظيمية.</t>
+    <t>يحتوي هذا الملف على ورقة بيانات واحدة: "الهيكل التنظيمي" — المستويات والمناصب والتسكين.</t>
+  </si>
+  <si>
+    <t>الأعمدة الإلزامية: المستوى، الرمز، الوحدة التنظيمية.</t>
   </si>
   <si>
     <t>ملاحظات مهمة:</t>
   </si>
   <si>
-    <t>- الصف الثاني في كل ورقة (المظلَّل بالأصفر) هو صف مثال فقط — يجب حذفه أو استبداله ببياناتك الحقيقية قبل الرفع.</t>
-  </si>
-  <si>
-    <t>- "الرمز" في ورقة الهيكل التنظيمي يجب أن يكون فريدًا لكل منصب — يُستخدم لتحديث نفس المنصب عند إعادة الاستيراد بدل تكراره.</t>
+    <t>- الصف الثاني (المظلَّل بالأصفر) هو صف مثال فقط — يجب حذفه أو استبداله ببياناتك الحقيقية قبل الرفع.</t>
+  </si>
+  <si>
+    <t>- "الرمز" يجب أن يكون فريدًا لكل منصب — يُستخدم لتحديث نفس المنصب عند إعادة الاستيراد بدل تكراره.</t>
   </si>
   <si>
     <t>- "رمز التبعية" هو رمز المنصب الأب (اتركه فارغًا للمنصب الجذر الأعلى).</t>
   </si>
   <si>
-    <t>- "الرقم الوظيفي لمن يشغل المنصب" يجب أن يطابق قيمة EMPLOYEE NUMBER في ورقة Employees Data لنفس الموظف.</t>
-  </si>
-  <si>
-    <t>- "الادارة" في ورقة الموظفين تُطابَق تلقائيًا مع اسم الوحدة التنظيمية الموجود في النظام — الأقسام غير المطابَقة تُترك فارغة وتظهر في تقرير الاستيراد لتصحيحها لاحقًا.</t>
-  </si>
-  <si>
-    <t>- الأدوار المتاحة في عمود "الدور في النظام": الرئيس التنفيذي، رئيس تنفيذي، رئيس مباشر، عميد / مدير، لجنة التقييم، مدير الاستراتيجية، مدير الجدارات، مدير الموارد البشرية، مدير النظام، مرشد، مشرف ميداني، موظف. اتركه فارغًا إن لم ترغب بإسناد دور.</t>
-  </si>
-  <si>
-    <t>- يمكن إعادة رفع نفس الملف بعد التعديل: يُحدَّث الموظفون بالرقم الوظيفي، وتُحدَّث المناصب بالرمز، ولا يُحذف أي تسكين أو دور موجود مسبقًا.</t>
-  </si>
-  <si>
-    <t>EMPLOYEE NUMBER</t>
-  </si>
-  <si>
-    <t>اسم الموظف</t>
-  </si>
-  <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>EMAIL ID</t>
-  </si>
-  <si>
-    <t>Hire Date</t>
-  </si>
-  <si>
-    <t>Qualification</t>
-  </si>
-  <si>
-    <t>Education Speciality</t>
-  </si>
-  <si>
-    <t>DATE OF BIRTH (YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>MARITIAL STATUS</t>
-  </si>
-  <si>
-    <t>GENDER</t>
-  </si>
-  <si>
-    <t>NATIONALITY</t>
-  </si>
-  <si>
-    <t>الادارة</t>
-  </si>
-  <si>
-    <t>اسم الوظيفة</t>
-  </si>
-  <si>
-    <t>POSITION</t>
-  </si>
-  <si>
-    <t>GRADE CODE</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Insurance Category</t>
-  </si>
-  <si>
-    <t>الدور في النظام</t>
+    <t>- "الرقم الوظيفي لمن يشغل المنصب" يجب أن يطابق EMPLOYEE NUMBER لموظف موجود بالفعل في النظام — هذا الملف لا يُنشئ موظفين جدد.</t>
+  </si>
+  <si>
+    <t>- يمكن إعادة رفع نفس الملف بعد التعديل: تُحدَّث المناصب بالرمز، ولا يُحذف أي تسكين موجود مسبقًا.</t>
+  </si>
+  <si>
+    <t>المستوى</t>
+  </si>
+  <si>
+    <t>الرمز</t>
+  </si>
+  <si>
+    <t>الوحدة التنظيمية</t>
+  </si>
+  <si>
+    <t>Organizational Unit</t>
+  </si>
+  <si>
+    <t>رمز التبعية</t>
+  </si>
+  <si>
+    <t>الرقم الوظيفي لمن يشغل المنصب</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>الرئيس التنفيذي</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>مدير إدارة رأس المال البشري</t>
+  </si>
+  <si>
+    <t>HR Director</t>
   </si>
   <si>
     <t>90010</t>
-  </si>
-  <si>
-    <t>سارة أحمد القحطاني</t>
-  </si>
-  <si>
-    <t>Sarah Ahmed Alqahtani</t>
-  </si>
-  <si>
-    <t>sarah.example@sr.edu.sa</t>
-  </si>
-  <si>
-    <t>2024-01-15</t>
-  </si>
-  <si>
-    <t>بكالوريوس</t>
-  </si>
-  <si>
-    <t>إدارة أعمال</t>
-  </si>
-  <si>
-    <t>1995-03-20</t>
-  </si>
-  <si>
-    <t>0501234567</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Saudi</t>
-  </si>
-  <si>
-    <t>إدارة رأس المال البشري</t>
-  </si>
-  <si>
-    <t>أخصائي موارد بشرية</t>
-  </si>
-  <si>
-    <t>HR Specialist</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Administrative</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>موظف</t>
-  </si>
-  <si>
-    <t>المستوى</t>
-  </si>
-  <si>
-    <t>الرمز</t>
-  </si>
-  <si>
-    <t>الوحدة التنظيمية</t>
-  </si>
-  <si>
-    <t>Organizational Unit</t>
-  </si>
-  <si>
-    <t>رمز التبعية</t>
-  </si>
-  <si>
-    <t>الرقم الوظيفي لمن يشغل المنصب</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>الرئيس التنفيذي</t>
-  </si>
-  <si>
-    <t>CEO</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>مدير إدارة رأس المال البشري</t>
-  </si>
-  <si>
-    <t>HR Director</t>
   </si>
 </sst>
 </file>
@@ -264,14 +143,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -614,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -626,68 +500,53 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -698,202 +557,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="19" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>56</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>32</v>
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
